--- a/artfynd/A 26482-2023 artfynd.xlsx
+++ b/artfynd/A 26482-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 26482-2023 artfynd.xlsx
+++ b/artfynd/A 26482-2023 artfynd.xlsx
@@ -916,7 +916,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118579119</v>
+        <v>118579127</v>
       </c>
       <c r="B4" t="n">
         <v>57290</v>
@@ -952,7 +952,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -961,10 +961,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>527272</v>
+        <v>527300</v>
       </c>
       <c r="R4" t="n">
-        <v>7026965</v>
+        <v>7026919</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1023,7 +1023,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118579122</v>
+        <v>118579119</v>
       </c>
       <c r="B5" t="n">
         <v>57290</v>
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>527287</v>
+        <v>527272</v>
       </c>
       <c r="R5" t="n">
-        <v>7026950</v>
+        <v>7026965</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1130,7 +1130,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118579114</v>
+        <v>118579117</v>
       </c>
       <c r="B6" t="n">
         <v>57290</v>
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527255</v>
+        <v>527266</v>
       </c>
       <c r="R6" t="n">
-        <v>7026999</v>
+        <v>7026977</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1237,7 +1237,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118579117</v>
+        <v>118579114</v>
       </c>
       <c r="B7" t="n">
         <v>57290</v>
@@ -1282,10 +1282,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>527266</v>
+        <v>527255</v>
       </c>
       <c r="R7" t="n">
-        <v>7026977</v>
+        <v>7026999</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,7 +1344,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118579127</v>
+        <v>118579122</v>
       </c>
       <c r="B8" t="n">
         <v>57290</v>
@@ -1380,7 +1380,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>527300</v>
+        <v>527287</v>
       </c>
       <c r="R8" t="n">
-        <v>7026919</v>
+        <v>7026950</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 26482-2023 artfynd.xlsx
+++ b/artfynd/A 26482-2023 artfynd.xlsx
@@ -809,7 +809,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118579113</v>
+        <v>118579122</v>
       </c>
       <c r="B3" t="n">
         <v>57290</v>
@@ -854,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>527253</v>
+        <v>527287</v>
       </c>
       <c r="R3" t="n">
-        <v>7027007</v>
+        <v>7026950</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -916,7 +916,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118579127</v>
+        <v>118579119</v>
       </c>
       <c r="B4" t="n">
         <v>57290</v>
@@ -952,7 +952,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -961,10 +961,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>527300</v>
+        <v>527272</v>
       </c>
       <c r="R4" t="n">
-        <v>7026919</v>
+        <v>7026965</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1023,7 +1023,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118579119</v>
+        <v>118579113</v>
       </c>
       <c r="B5" t="n">
         <v>57290</v>
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>527272</v>
+        <v>527253</v>
       </c>
       <c r="R5" t="n">
-        <v>7026965</v>
+        <v>7027007</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1130,7 +1130,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118579117</v>
+        <v>118579127</v>
       </c>
       <c r="B6" t="n">
         <v>57290</v>
@@ -1166,7 +1166,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527266</v>
+        <v>527300</v>
       </c>
       <c r="R6" t="n">
-        <v>7026977</v>
+        <v>7026919</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1237,7 +1237,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118579114</v>
+        <v>118579117</v>
       </c>
       <c r="B7" t="n">
         <v>57290</v>
@@ -1282,10 +1282,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>527255</v>
+        <v>527266</v>
       </c>
       <c r="R7" t="n">
-        <v>7026999</v>
+        <v>7026977</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,7 +1344,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118579122</v>
+        <v>118579114</v>
       </c>
       <c r="B8" t="n">
         <v>57290</v>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>527287</v>
+        <v>527255</v>
       </c>
       <c r="R8" t="n">
-        <v>7026950</v>
+        <v>7026999</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 26482-2023 artfynd.xlsx
+++ b/artfynd/A 26482-2023 artfynd.xlsx
@@ -809,7 +809,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118579122</v>
+        <v>118579113</v>
       </c>
       <c r="B3" t="n">
         <v>57290</v>
@@ -854,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>527287</v>
+        <v>527253</v>
       </c>
       <c r="R3" t="n">
-        <v>7026950</v>
+        <v>7027007</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -916,7 +916,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118579119</v>
+        <v>118579127</v>
       </c>
       <c r="B4" t="n">
         <v>57290</v>
@@ -952,7 +952,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -961,10 +961,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>527272</v>
+        <v>527300</v>
       </c>
       <c r="R4" t="n">
-        <v>7026965</v>
+        <v>7026919</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1023,7 +1023,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118579113</v>
+        <v>118579114</v>
       </c>
       <c r="B5" t="n">
         <v>57290</v>
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>527253</v>
+        <v>527255</v>
       </c>
       <c r="R5" t="n">
-        <v>7027007</v>
+        <v>7026999</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1130,7 +1130,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118579127</v>
+        <v>118579122</v>
       </c>
       <c r="B6" t="n">
         <v>57290</v>
@@ -1166,7 +1166,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527300</v>
+        <v>527287</v>
       </c>
       <c r="R6" t="n">
-        <v>7026919</v>
+        <v>7026950</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1237,7 +1237,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118579117</v>
+        <v>118579129</v>
       </c>
       <c r="B7" t="n">
         <v>57290</v>
@@ -1273,7 +1273,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1282,10 +1282,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>527266</v>
+        <v>527303</v>
       </c>
       <c r="R7" t="n">
-        <v>7026977</v>
+        <v>7026910</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,7 +1344,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118579114</v>
+        <v>118579119</v>
       </c>
       <c r="B8" t="n">
         <v>57290</v>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>527255</v>
+        <v>527272</v>
       </c>
       <c r="R8" t="n">
-        <v>7026999</v>
+        <v>7026965</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1451,7 +1451,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118579129</v>
+        <v>118579117</v>
       </c>
       <c r="B9" t="n">
         <v>57290</v>
@@ -1487,7 +1487,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>527303</v>
+        <v>527266</v>
       </c>
       <c r="R9" t="n">
-        <v>7026910</v>
+        <v>7026977</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 26482-2023 artfynd.xlsx
+++ b/artfynd/A 26482-2023 artfynd.xlsx
@@ -809,7 +809,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118579113</v>
+        <v>118579119</v>
       </c>
       <c r="B3" t="n">
         <v>57290</v>
@@ -854,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>527253</v>
+        <v>527272</v>
       </c>
       <c r="R3" t="n">
-        <v>7027007</v>
+        <v>7026965</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -916,7 +916,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118579127</v>
+        <v>118579117</v>
       </c>
       <c r="B4" t="n">
         <v>57290</v>
@@ -952,7 +952,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -961,10 +961,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>527300</v>
+        <v>527266</v>
       </c>
       <c r="R4" t="n">
-        <v>7026919</v>
+        <v>7026977</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1023,7 +1023,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118579114</v>
+        <v>118579127</v>
       </c>
       <c r="B5" t="n">
         <v>57290</v>
@@ -1059,7 +1059,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>527255</v>
+        <v>527300</v>
       </c>
       <c r="R5" t="n">
-        <v>7026999</v>
+        <v>7026919</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1130,7 +1130,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118579122</v>
+        <v>118579113</v>
       </c>
       <c r="B6" t="n">
         <v>57290</v>
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527287</v>
+        <v>527253</v>
       </c>
       <c r="R6" t="n">
-        <v>7026950</v>
+        <v>7027007</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1237,7 +1237,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118579129</v>
+        <v>118579114</v>
       </c>
       <c r="B7" t="n">
         <v>57290</v>
@@ -1273,7 +1273,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1282,10 +1282,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>527303</v>
+        <v>527255</v>
       </c>
       <c r="R7" t="n">
-        <v>7026910</v>
+        <v>7026999</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,7 +1344,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118579119</v>
+        <v>118579122</v>
       </c>
       <c r="B8" t="n">
         <v>57290</v>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>527272</v>
+        <v>527287</v>
       </c>
       <c r="R8" t="n">
-        <v>7026965</v>
+        <v>7026950</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1451,7 +1451,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118579117</v>
+        <v>118579129</v>
       </c>
       <c r="B9" t="n">
         <v>57290</v>
@@ -1487,7 +1487,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>527266</v>
+        <v>527303</v>
       </c>
       <c r="R9" t="n">
-        <v>7026977</v>
+        <v>7026910</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 26482-2023 artfynd.xlsx
+++ b/artfynd/A 26482-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>344851</v>
       </c>
       <c r="B2" t="n">
-        <v>89391</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>527273.6238105062</v>
+        <v>527274</v>
       </c>
       <c r="R2" t="n">
-        <v>7026983.949069157</v>
+        <v>7026984</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,19 +752,9 @@
           <t>2009-10-29</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2009-10-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -809,15 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118579114</v>
+        <v>353859</v>
       </c>
       <c r="B3" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -825,39 +805,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fagerbrännan (Fagerbrännan), Jmt</t>
+          <t>S Långflon, Fagerbrännan/Långtjärnberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>527255</v>
+        <v>527268</v>
       </c>
       <c r="R3" t="n">
-        <v>7026999</v>
+        <v>7027016</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,12 +868,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-20</t>
+          <t>2009-10-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-20</t>
+          <t>2009-10-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,31 +884,39 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AN3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Joel Schill</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Joel Schill</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118579117</v>
+        <v>353860</v>
       </c>
       <c r="B4" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -932,39 +924,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fagerbrännan (Fagerbrännan), Jmt</t>
+          <t>Fagerbrännan, Långtjärnberget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>527266</v>
+        <v>527308</v>
       </c>
       <c r="R4" t="n">
-        <v>7026977</v>
+        <v>7026946</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,12 +987,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-07-20</t>
+          <t>2009-10-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-07-20</t>
+          <t>2009-10-29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,31 +1003,39 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AN4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Joel Schill</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Joel Schill</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118579129</v>
+        <v>865907</v>
       </c>
       <c r="B5" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,39 +1043,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fagerbrännan (Fagerbrännan), Jmt</t>
+          <t>Fagerbrännan, Långtjärnberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>527303</v>
+        <v>527362</v>
       </c>
       <c r="R5" t="n">
-        <v>7026910</v>
+        <v>7026366</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,12 +1106,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-07-20</t>
+          <t>2009-10-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-07-20</t>
+          <t>2009-10-29</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Vid liten myr</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,71 +1127,79 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AN5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>1 substratenheter # sälgbark</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Joel Schill</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Joel Schill</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118579113</v>
+        <v>118579125</v>
       </c>
       <c r="B6" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fagerbrännan (Fagerbrännan), Jmt</t>
+          <t>Fagerbrännan, Fagerbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527253</v>
+        <v>527300</v>
       </c>
       <c r="R6" t="n">
-        <v>7027007</v>
+        <v>7026975</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1237,15 +1258,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118579119</v>
+        <v>1956275</v>
       </c>
       <c r="B7" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1253,39 +1269,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fagerbrännan (Fagerbrännan), Jmt</t>
+          <t>Fagerbrännan, Långtjärnberget, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>527272</v>
+        <v>527362</v>
       </c>
       <c r="R7" t="n">
-        <v>7026965</v>
+        <v>7026366</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,12 +1332,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-07-20</t>
+          <t>2009-10-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-07-20</t>
+          <t>2009-10-29</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Vid liten myr</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1328,31 +1353,39 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AN7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>1 substratenheter # sälgbark</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Joel Schill</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Joel Schill</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118579122</v>
+        <v>118579103</v>
       </c>
       <c r="B8" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1380,19 +1413,19 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fagerbrännan (Fagerbrännan), Jmt</t>
+          <t>Fagerbrännan, Fagerbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>527287</v>
+        <v>527247</v>
       </c>
       <c r="R8" t="n">
-        <v>7026950</v>
+        <v>7027051</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1451,15 +1484,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118579127</v>
+        <v>118579113</v>
       </c>
       <c r="B9" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1487,19 +1515,19 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fagerbrännan (Fagerbrännan), Jmt</t>
+          <t>Fagerbrännan, Fagerbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>527300</v>
+        <v>527253</v>
       </c>
       <c r="R9" t="n">
-        <v>7026919</v>
+        <v>7027007</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1555,6 +1583,720 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>118579114</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Fagerbrännan, Fagerbrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>527255</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7026999</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Joel Schill</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Joel Schill</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>118579117</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Fagerbrännan, Fagerbrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>527266</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7026977</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Joel Schill</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Joel Schill</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>118579119</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Fagerbrännan, Fagerbrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>527272</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7026965</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Joel Schill</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Joel Schill</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>118579122</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Fagerbrännan, Fagerbrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>527287</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7026950</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Joel Schill</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Joel Schill</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>118579127</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Fagerbrännan, Fagerbrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>527300</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7026919</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Joel Schill</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Joel Schill</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>118579129</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Fagerbrännan, Fagerbrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>527303</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7026910</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Joel Schill</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Joel Schill</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>118579133</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Fagerbrännan, Fagerbrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>527331</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7026887</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Joel Schill</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Joel Schill</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26482-2023 artfynd.xlsx
+++ b/artfynd/A 26482-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/344851</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,6 +920,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/353859</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1029,6 +1044,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/353860</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1153,6 +1173,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/865907</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1255,6 +1280,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118579125</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1379,6 +1409,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1956275</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1481,6 +1516,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118579103</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1583,6 +1623,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118579113</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1685,6 +1730,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118579114</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1787,6 +1837,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118579117</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1889,6 +1944,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118579119</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1991,6 +2051,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118579122</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2093,6 +2158,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118579127</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2195,6 +2265,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118579129</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2297,8 +2372,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118579133</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>